--- a/learn-english.xlsx
+++ b/learn-english.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11108"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10808"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreadipaola/Documents/GitHub/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreadipaola/Documents/GitHub/responsive-design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C51794C-4FEA-BD43-AB66-639CC3E6F95D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E6CAF5-B5D2-0D4B-86C2-A61464AC02FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29040" yWindow="9000" windowWidth="21040" windowHeight="17440" xr2:uid="{7364E0F6-D0AA-D842-BE53-618D0A6AFC46}"/>
+    <workbookView xWindow="14080" yWindow="1600" windowWidth="14720" windowHeight="16260" xr2:uid="{7364E0F6-D0AA-D842-BE53-618D0A6AFC46}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>English</t>
   </si>
@@ -127,6 +127,60 @@
   </si>
   <si>
     <t>would suffice</t>
+  </si>
+  <si>
+    <t>larger</t>
+  </si>
+  <si>
+    <t>più grandi</t>
+  </si>
+  <si>
+    <t>likewise</t>
+  </si>
+  <si>
+    <t>allo stesso modo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comes in </t>
+  </si>
+  <si>
+    <t>entra in gioco</t>
+  </si>
+  <si>
+    <t>all of this</t>
+  </si>
+  <si>
+    <t>tutto ciò</t>
+  </si>
+  <si>
+    <t>as long as</t>
+  </si>
+  <si>
+    <t>fino a qundo</t>
+  </si>
+  <si>
+    <t>works just fine</t>
+  </si>
+  <si>
+    <t>funziona bene</t>
+  </si>
+  <si>
+    <t>art direction</t>
+  </si>
+  <si>
+    <t>direzione artistica</t>
+  </si>
+  <si>
+    <t>be just fine</t>
+  </si>
+  <si>
+    <t>essere apposto</t>
+  </si>
+  <si>
+    <t>wouldn't it be great</t>
+  </si>
+  <si>
+    <t>non sarebbe fanstastico</t>
   </si>
 </sst>
 </file>
@@ -214,7 +268,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -230,7 +284,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -526,7 +580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8F3ACB1-4208-5A47-A40E-2A91A8F2B8B9}">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="70.1640625" customWidth="1"/>
@@ -669,6 +723,78 @@
         <v>32</v>
       </c>
     </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" t="s">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/learn-english.xlsx
+++ b/learn-english.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreadipaola/Documents/GitHub/responsive-design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E6CAF5-B5D2-0D4B-86C2-A61464AC02FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E61937F2-A8EE-BE40-9F5E-779C0A26D870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14080" yWindow="1600" windowWidth="14720" windowHeight="16260" xr2:uid="{7364E0F6-D0AA-D842-BE53-618D0A6AFC46}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>English</t>
   </si>
@@ -181,6 +181,12 @@
   </si>
   <si>
     <t>non sarebbe fanstastico</t>
+  </si>
+  <si>
+    <t>scuffles back</t>
+  </si>
+  <si>
+    <t>rimoscolano</t>
   </si>
 </sst>
 </file>
@@ -580,7 +586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8F3ACB1-4208-5A47-A40E-2A91A8F2B8B9}">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="70.1640625" customWidth="1"/>
@@ -795,6 +801,14 @@
         <v>51</v>
       </c>
     </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" t="s">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/learn-english.xlsx
+++ b/learn-english.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andreadipaola/Documents/GitHub/responsive-design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E61937F2-A8EE-BE40-9F5E-779C0A26D870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB051F8D-CDD4-5541-8EBE-E4564D7E0107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14080" yWindow="1600" windowWidth="14720" windowHeight="16260" xr2:uid="{7364E0F6-D0AA-D842-BE53-618D0A6AFC46}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>English</t>
   </si>
@@ -187,6 +187,12 @@
   </si>
   <si>
     <t>rimoscolano</t>
+  </si>
+  <si>
+    <t>convery</t>
+  </si>
+  <si>
+    <t>trasportare</t>
   </si>
 </sst>
 </file>
@@ -586,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8F3ACB1-4208-5A47-A40E-2A91A8F2B8B9}">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="70.1640625" customWidth="1"/>
@@ -809,6 +815,14 @@
         <v>53</v>
       </c>
     </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" t="s">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
